--- a/MATH/M09/bus123-math-m09-l02-starter.xlsx
+++ b/MATH/M09/bus123-math-m09-l02-starter.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R8e17dd49d95e494b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R487bc27381684e32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R14d9bd77461b4ac1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R970a89dd1add46e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R6abae20d36d34a75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Rb5db8f38f1804fc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="Ree4243c242f04866"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R327f4bb83b834f85"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,11 +16,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <x:numFmt numFmtId="200" formatCode="@"/>
+    <x:numFmt numFmtId="201" formatCode="0.00%"/>
   </x:numFmts>
-  <x:fonts count="10">
+  <x:fonts count="19">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -70,8 +71,57 @@
       <x:color rgb="FF355773"/>
       <x:name val="DM Sans"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1A1F2C"/>
+      <x:name val="DM Sans"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:color rgb="FF1A1F2C"/>
+      <x:name val="DM Sans"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1A1F2C"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF355773"/>
+      <x:name val="DM Sans"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1A1F2C"/>
+      <x:name val="DM Sans"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="DM Sans"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="DM Sans"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF355773"/>
+      <x:name val="DM Sans"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1A1F2C"/>
+      <x:name val="DM Sans"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="24">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -118,8 +168,78 @@
         <x:fgColor rgb="FFEAF3EC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFD966"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4A7C5E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFD966"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4A7C5E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFD966"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4A7C5E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="4">
+  <x:borders count="16">
     <x:border/>
     <x:border>
       <x:bottom style="thin">
@@ -136,11 +256,146 @@
         <x:color rgb="FFD9E2D0"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="FF355773"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF355773"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF355773"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="FF355773"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF355773"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="FF355773"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF355773"/>
+      </x:right>
+      <x:bottom style="medium">
+        <x:color rgb="FF355773"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="158">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -218,10 +473,463 @@
     <x:xf numFmtId="200" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="5" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="5" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="5" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="15" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="5" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="10" fontId="5" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="15" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="10" fontId="13" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="17" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="15" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="15" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="17" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="15" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="15" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="17" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="19" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="19" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="19" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="20" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="5" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="17" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="15" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="15" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="17" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="6">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF1A6B3C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C4A2B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF1A6B3C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C4A2B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF1A6B3C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C4A2B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
   <x:colors>
     <x:indexedColors>
       <x:rgbColor rgb="00000000"/>
@@ -567,10 +1275,8 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open the slide deck and stop at each Live You Try It pause.</x:t>
-        </x:is>
+      <x:c r="B5" s="2" t="str">
+        <x:v>Open the slide deck and workbook before class; use the slide number in Live You Try It to find each pause.</x:v>
       </x:c>
       <x:c r="C5" s="2" t="n"/>
       <x:c r="D5" s="2" t="n"/>
@@ -583,10 +1289,8 @@
           <x:t xml:space="preserve">2</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Enter the slide givens into the yellow input cells first.</x:t>
-        </x:is>
+      <x:c r="B6" s="2" t="str">
+        <x:v>Cells labeled INPUT use yellow fill. Enter the scenario givens there before building a formula.</x:v>
       </x:c>
       <x:c r="C6" s="2" t="n"/>
       <x:c r="D6" s="2" t="n"/>
@@ -599,10 +1303,8 @@
           <x:t xml:space="preserve">3</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Build formulas by referencing the input cells. Do not type numbers inside formulas.</x:t>
-        </x:is>
+      <x:c r="B7" s="2" t="str">
+        <x:v>Cells labeled FORMULA / RESULT use blue fill. Build formulas with cell references; do not type the answer as a constant.</x:v>
       </x:c>
       <x:c r="C7" s="2" t="n"/>
       <x:c r="D7" s="2" t="n"/>
@@ -615,10 +1317,8 @@
           <x:t xml:space="preserve">4</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use the feedback cells to revise your Live You Try It work.</x:t>
-        </x:is>
+      <x:c r="B8" s="2" t="str">
+        <x:v>Feedback checks the formula, required references, and value. A hardcoded value does not count as complete.</x:v>
       </x:c>
       <x:c r="C8" s="2" t="n"/>
       <x:c r="D8" s="2" t="n"/>
@@ -631,10 +1331,8 @@
           <x:t xml:space="preserve">5</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Complete Class Challenge with formulas. The blue answer cells start blank in the public starter.</x:t>
-        </x:is>
+      <x:c r="B9" s="2" t="str">
+        <x:v>Class Challenge deliverable: loan-term evidence, equal-contribution transfer formulas, and two written recommendations.</x:v>
       </x:c>
       <x:c r="C9" s="2" t="n"/>
       <x:c r="D9" s="2" t="n"/>
@@ -718,24 +1416,28 @@
       <x:c r="F15" s="2" t="n"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="2" t="n"/>
-      <x:c r="B16" s="2" t="n"/>
+      <x:c r="A16" s="119" t="str">
+        <x:v>Accessibility cue</x:v>
+      </x:c>
+      <x:c r="B16" s="119" t="str">
+        <x:v>INPUT, FORMULA / RESULT, and FEEDBACK labels carry the meaning even if color is unavailable.</x:v>
+      </x:c>
       <x:c r="C16" s="2" t="n"/>
       <x:c r="D16" s="2" t="n"/>
       <x:c r="E16" s="2" t="n"/>
       <x:c r="F16" s="2" t="n"/>
     </x:row>
-    <x:row r="17" ht="22" customHeight="1">
-      <x:c r="A17" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">I Can</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B17" s="15" t="n"/>
-      <x:c r="C17" s="15" t="n"/>
-      <x:c r="D17" s="15" t="n"/>
-      <x:c r="E17" s="15" t="n"/>
-      <x:c r="F17" s="15" t="n"/>
+    <x:row r="17" ht="32" customHeight="1">
+      <x:c r="A17" s="154" t="str">
+        <x:v>Model boundary</x:v>
+      </x:c>
+      <x:c r="B17" s="155" t="str">
+        <x:v>Loan models use financed principal, a fixed nominal rate, level payments, and exclude taxes, insurance, fees, and prepayment.</x:v>
+      </x:c>
+      <x:c r="C17" s="155" t="n"/>
+      <x:c r="D17" s="155" t="n"/>
+      <x:c r="E17" s="155" t="n"/>
+      <x:c r="F17" s="155" t="n"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="2" t="n">
@@ -806,8 +1508,8 @@
     <x:mergeCell ref="A2:F2"/>
     <x:mergeCell ref="A11:F11"/>
     <x:mergeCell ref="A1:F1"/>
-    <x:mergeCell ref="A17:F17"/>
     <x:mergeCell ref="A4:F4"/>
+    <x:mergeCell ref="B17:F17"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -890,335 +1592,313 @@
       <x:c r="J4" s="15" t="n"/>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pause</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Slide</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Build This</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Your Formula / Answer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Formula Hint</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Feedback</x:t>
-        </x:is>
+      <x:c r="A5" s="7" t="str">
+        <x:v>Pause</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="str">
+        <x:v>Slide</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="str">
+        <x:v>Build This</x:v>
+      </x:c>
+      <x:c r="D5" s="7" t="str">
+        <x:v>Amount / Payment</x:v>
+      </x:c>
+      <x:c r="E5" s="7" t="str">
+        <x:v>Annual Rate</x:v>
+      </x:c>
+      <x:c r="F5" s="7" t="str">
+        <x:v>Years</x:v>
+      </x:c>
+      <x:c r="G5" s="7" t="str">
+        <x:v>Periods / Year</x:v>
+      </x:c>
+      <x:c r="H5" s="7" t="str">
+        <x:v>FORMULA / RESULT</x:v>
+      </x:c>
+      <x:c r="I5" s="7" t="str">
+        <x:v>Formula Hint</x:v>
+      </x:c>
+      <x:c r="J5" s="7" t="str">
+        <x:v>FEEDBACK</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mortgage</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">07</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Calculate monthly payment for the worked mortgage.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" s="8" t="n"/>
-      <x:c r="E6" s="8" t="n"/>
-      <x:c r="F6" s="8" t="n"/>
-      <x:c r="G6" s="8" t="n"/>
-      <x:c r="H6" s="9" t="n"/>
-      <x:c r="I6" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use monthly rate and total months.</x:t>
-        </x:is>
+      <x:c r="A6" s="2" t="str">
+        <x:v>Mortgage</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C6" s="2" t="str">
+        <x:v>Calculate the monthly payment for the instructor model.</x:v>
+      </x:c>
+      <x:c r="D6" s="122" t="n">
+        <x:v>320000</x:v>
+      </x:c>
+      <x:c r="E6" s="123" t="n">
+        <x:v>0.065</x:v>
+      </x:c>
+      <x:c r="F6" s="124" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G6" s="124" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H6" s="128"/>
+      <x:c r="I6" s="10" t="str">
+        <x:v>Use monthly rate and total months in PMT.</x:v>
       </x:c>
       <x:c r="J6" s="11" t="str">
-        <x:f>IF(H6="","Enter the PMT formula.",IF(ABS(H6+2022.62)&lt;0.02,"Correct - payment is about $2,022.62 outflow.","Check monthly rate, total months, and signs."))</x:f>
+        <x:f>IF(H6="","Enter the PMT formula.",IF(NOT(ISFORMULA(H6)),"Correct values must be built with a formula.",IF(AND(ABS(H6-(-2022.617675))&lt;0.02,ISNUMBER(SEARCH("D6",FORMULATEXT(H6))),ISNUMBER(SEARCH("E6",FORMULATEXT(H6))),ISNUMBER(SEARCH("F6",FORMULATEXT(H6))),ISNUMBER(SEARCH("G6",FORMULATEXT(H6)))),"Correct formula, references, and value.","Check D6:G6, monthly timing, and borrower-perspective signs.")))</x:f>
         <x:v>Enter the PMT formula.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mortgage</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">07</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Calculate total paid over the loan.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" s="8" t="n"/>
-      <x:c r="E7" s="8" t="n"/>
-      <x:c r="F7" s="8" t="n"/>
-      <x:c r="G7" s="8" t="n"/>
-      <x:c r="H7" s="9" t="n"/>
-      <x:c r="I7" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ABS(monthly PMT) times total payments.</x:t>
-        </x:is>
+      <x:c r="A7" s="2" t="str">
+        <x:v>Mortgage</x:v>
+      </x:c>
+      <x:c r="B7" s="2" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="str">
+        <x:v>Calculate total paid over the loan.</x:v>
+      </x:c>
+      <x:c r="D7" s="125" t="n">
+        <x:v>320000</x:v>
+      </x:c>
+      <x:c r="E7" s="126" t="n">
+        <x:v>0.065</x:v>
+      </x:c>
+      <x:c r="F7" s="127" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G7" s="127" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H7" s="129"/>
+      <x:c r="I7" s="10" t="str">
+        <x:v>Use the payment cell and the period inputs.</x:v>
       </x:c>
       <x:c r="J7" s="11" t="str">
-        <x:f>IF(H7="","Enter the total-paid formula.",IF(ABS(H7-728142.36)&lt;2,"Correct - total paid is about $728,142.","Use the payment from row 6 and total months."))</x:f>
+        <x:f>IF(H7="","Enter the total-paid formula.",IF(NOT(ISFORMULA(H7)),"Correct values must be built with a formula.",IF(AND(ABS(H7-(728142.363))&lt;0.02,ISNUMBER(SEARCH("H6",FORMULATEXT(H7))),ISNUMBER(SEARCH("F7",FORMULATEXT(H7))),ISNUMBER(SEARCH("G7",FORMULATEXT(H7)))),"Correct formula, references, and value.","Reference H6 and the period inputs; keep the unrounded payment.")))</x:f>
         <x:v>Enter the total-paid formula.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mortgage</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">07</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Calculate total interest.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" s="8" t="n"/>
-      <x:c r="E8" s="8" t="n"/>
-      <x:c r="F8" s="8" t="n"/>
-      <x:c r="G8" s="8" t="n"/>
-      <x:c r="H8" s="9" t="n"/>
-      <x:c r="I8" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Total paid minus original loan.</x:t>
-        </x:is>
+      <x:c r="A8" s="2" t="str">
+        <x:v>Mortgage</x:v>
+      </x:c>
+      <x:c r="B8" s="2" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="str">
+        <x:v>Calculate total interest.</x:v>
+      </x:c>
+      <x:c r="D8" s="125" t="n">
+        <x:v>320000</x:v>
+      </x:c>
+      <x:c r="E8" s="126" t="n">
+        <x:v>0.065</x:v>
+      </x:c>
+      <x:c r="F8" s="127" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G8" s="127" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H8" s="129"/>
+      <x:c r="I8" s="10" t="str">
+        <x:v>Reference total paid and principal.</x:v>
       </x:c>
       <x:c r="J8" s="11" t="str">
-        <x:f>IF(H8="","Enter the total-interest formula.",IF(ABS(H8-408142.36)&lt;2,"Correct - interest is about $408,142.","Subtract the original loan amount."))</x:f>
+        <x:f>IF(H8="","Enter the total-interest formula.",IF(NOT(ISFORMULA(H8)),"Correct values must be built with a formula.",IF(AND(ABS(H8-(408142.363))&lt;0.02,ISNUMBER(SEARCH("H7",FORMULATEXT(H8))),ISNUMBER(SEARCH("D8",FORMULATEXT(H8)))),"Correct formula, references, and value.","Subtract the principal in D8 from total paid in H7.")))</x:f>
         <x:v>Enter the total-interest formula.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savings</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">08</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Project retirement value from monthly deposits.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" s="8" t="n"/>
-      <x:c r="E9" s="8" t="n"/>
-      <x:c r="F9" s="8" t="n"/>
-      <x:c r="G9" s="8" t="n"/>
-      <x:c r="H9" s="9" t="n"/>
-      <x:c r="I9" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Monthly contribution is negative in =FV().</x:t>
-        </x:is>
+      <x:c r="A9" s="2" t="str">
+        <x:v>Savings</x:v>
+      </x:c>
+      <x:c r="B9" s="2" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="str">
+        <x:v>Project retirement value from monthly deposits.</x:v>
+      </x:c>
+      <x:c r="D9" s="125" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E9" s="126" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+      <x:c r="F9" s="127" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G9" s="127" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H9" s="129"/>
+      <x:c r="I9" s="10" t="str">
+        <x:v>Monthly contribution is an outflow in FV.</x:v>
       </x:c>
       <x:c r="J9" s="11" t="str">
-        <x:f>IF(H9="","Enter the FV formula.",IF(ABS(H9-609985.50)&lt;0.5,"Correct - future value matches the formula result.","Check pmt sign and monthly timing."))</x:f>
+        <x:f>IF(H9="","Enter the FV formula.",IF(NOT(ISFORMULA(H9)),"Correct values must be built with a formula.",IF(AND(ABS(H9-(609985.5))&lt;0.02,ISNUMBER(SEARCH("D9",FORMULATEXT(H9))),ISNUMBER(SEARCH("E9",FORMULATEXT(H9))),ISNUMBER(SEARCH("F9",FORMULATEXT(H9))),ISNUMBER(SEARCH("G9",FORMULATEXT(H9)))),"Correct formula, references, and value.","Use D9:G9 and treat the monthly contribution as an outflow.")))</x:f>
         <x:v>Enter the FV formula.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savings</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">08</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Calculate total contributed.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" s="8" t="n"/>
-      <x:c r="E10" s="8" t="n"/>
-      <x:c r="F10" s="8" t="n"/>
-      <x:c r="G10" s="8" t="n"/>
-      <x:c r="H10" s="9" t="n"/>
-      <x:c r="I10" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Monthly deposit times total months.</x:t>
-        </x:is>
+      <x:c r="A10" s="2" t="str">
+        <x:v>Savings</x:v>
+      </x:c>
+      <x:c r="B10" s="2" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="str">
+        <x:v>Calculate total contributed.</x:v>
+      </x:c>
+      <x:c r="D10" s="125" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E10" s="126" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+      <x:c r="F10" s="127" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G10" s="127" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H10" s="129"/>
+      <x:c r="I10" s="10" t="str">
+        <x:v>Monthly deposit times total months.</x:v>
       </x:c>
       <x:c r="J10" s="11" t="str">
-        <x:f>IF(H10="","Enter total contributed.",IF(ABS(H10-180000)&lt;0.01,"Correct - total contributed is $180,000.","Use contribution x years x 12."))</x:f>
+        <x:f>IF(H10="","Enter total contributed.",IF(NOT(ISFORMULA(H10)),"Correct values must be built with a formula.",IF(AND(ABS(H10-(180000))&lt;0.02,ISNUMBER(SEARCH("D10",FORMULATEXT(H10))),ISNUMBER(SEARCH("F10",FORMULATEXT(H10))),ISNUMBER(SEARCH("G10",FORMULATEXT(H10)))),"Correct formula, references, and value.","Multiply the contribution by years and periods per year.")))</x:f>
         <x:v>Enter total contributed.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Payment Stream</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">09</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Value the $1,500 monthly payment stream.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D11" s="8" t="n"/>
-      <x:c r="E11" s="8" t="n"/>
-      <x:c r="F11" s="8" t="n"/>
-      <x:c r="G11" s="8" t="n"/>
-      <x:c r="H11" s="9" t="n"/>
-      <x:c r="I11" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Payment received is positive; PV result is negative.</x:t>
-        </x:is>
+      <x:c r="A11" s="2" t="str">
+        <x:v>Payment Stream</x:v>
+      </x:c>
+      <x:c r="B11" s="2" t="str">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="str">
+        <x:v>Value the $1,500 monthly payment stream.</x:v>
+      </x:c>
+      <x:c r="D11" s="125" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="E11" s="126" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="F11" s="127" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G11" s="127" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H11" s="129"/>
+      <x:c r="I11" s="10" t="str">
+        <x:v>Payment received is positive; interpret the PV sign by perspective.</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str">
-        <x:f>IF(H11="","Enter the PV formula.",IF(ABS(H11+141422.03)&lt;2,"Correct - PV is about -$141,422.","Check sign and monthly discount rate."))</x:f>
+        <x:f>IF(H11="","Enter the PV formula.",IF(NOT(ISFORMULA(H11)),"Correct values must be built with a formula.",IF(AND(ABS(H11-(-141422.03))&lt;0.02,ISNUMBER(SEARCH("D11",FORMULATEXT(H11))),ISNUMBER(SEARCH("E11",FORMULATEXT(H11))),ISNUMBER(SEARCH("F11",FORMULATEXT(H11))),ISNUMBER(SEARCH("G11",FORMULATEXT(H11)))),"Correct formula, references, and value.","Use the received payment as positive and interpret the negative PV by perspective.")))</x:f>
         <x:v>Enter the PV formula.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Timing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ordinary annuity payment for $25,000 at 6% over 60 months.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D12" s="8" t="n"/>
-      <x:c r="E12" s="8" t="n"/>
-      <x:c r="F12" s="8" t="n"/>
-      <x:c r="G12" s="8" t="n"/>
-      <x:c r="H12" s="9" t="n"/>
-      <x:c r="I12" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">type=0 is ordinary annuity.</x:t>
-        </x:is>
+      <x:c r="A12" s="2" t="str">
+        <x:v>Timing</x:v>
+      </x:c>
+      <x:c r="B12" s="2" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C12" s="2" t="str">
+        <x:v>Ordinary annuity payment for $25,000 at 6% over 60 months.</x:v>
+      </x:c>
+      <x:c r="D12" s="125" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="E12" s="126" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="F12" s="127" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G12" s="127" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H12" s="129"/>
+      <x:c r="I12" s="10" t="str">
+        <x:v>Use type=0 for end-of-period payments.</x:v>
       </x:c>
       <x:c r="J12" s="11" t="str">
-        <x:f>IF(H12="","Enter ordinary annuity PMT.",IF(ABS(H12+483.32)&lt;0.02,"Correct - ordinary payment is about $483.32.","Use type 0 or omit type."))</x:f>
-        <x:v>Enter ordinary annuity PMT.</x:v>
+        <x:f>IF(H12="","Enter the ordinary-annuity PMT.",IF(NOT(ISFORMULA(H12)),"Correct values must be built with a formula.",IF(AND(ABS(H12-(-483.32))&lt;0.02,ISNUMBER(SEARCH("D12",FORMULATEXT(H12))),ISNUMBER(SEARCH("E12",FORMULATEXT(H12))),ISNUMBER(SEARCH("F12",FORMULATEXT(H12))),ISNUMBER(SEARCH("G12",FORMULATEXT(H12)))),"Correct formula, references, and value.","Use D12:G12 and type=0.")))</x:f>
+        <x:v>Enter the ordinary-annuity PMT.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Timing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Annuity due payment for the same loan.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" s="8" t="n"/>
-      <x:c r="E13" s="8" t="n"/>
-      <x:c r="F13" s="8" t="n"/>
-      <x:c r="G13" s="8" t="n"/>
-      <x:c r="H13" s="9" t="n"/>
-      <x:c r="I13" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">type=1 means beginning of period.</x:t>
-        </x:is>
+      <x:c r="A13" s="2" t="str">
+        <x:v>Timing</x:v>
+      </x:c>
+      <x:c r="B13" s="2" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="str">
+        <x:v>Annuity-due payment for the same loan.</x:v>
+      </x:c>
+      <x:c r="D13" s="125" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="E13" s="126" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="F13" s="127" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G13" s="127" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H13" s="130"/>
+      <x:c r="I13" s="10" t="str">
+        <x:v>Use type=1 for beginning-of-period payments.</x:v>
       </x:c>
       <x:c r="J13" s="11" t="str">
-        <x:f>IF(H13="","Enter annuity due PMT.",IF(ABS(H13+480.91)&lt;0.02,"Correct - annuity due payment is about $480.91.","Use type=1 for beginning-of-period payment."))</x:f>
-        <x:v>Enter annuity due PMT.</x:v>
+        <x:f>IF(H13="","Enter the annuity-due PMT.",IF(NOT(ISFORMULA(H13)),"Correct values must be built with a formula.",IF(AND(ABS(H13-(-480.92))&lt;0.02,ISNUMBER(SEARCH("D13",FORMULATEXT(H13))),ISNUMBER(SEARCH("E13",FORMULATEXT(H13))),ISNUMBER(SEARCH("F13",FORMULATEXT(H13))),ISNUMBER(SEARCH("G13",FORMULATEXT(H13)))),"Correct formula, references, and value.","Use D13:G13 and type=1.")))</x:f>
+        <x:v>Enter the annuity-due PMT.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="2" t="n"/>
-      <x:c r="B14" s="2" t="n"/>
-      <x:c r="C14" s="2" t="n"/>
-      <x:c r="D14" s="2" t="n"/>
-      <x:c r="E14" s="2" t="n"/>
-      <x:c r="F14" s="2" t="n"/>
-      <x:c r="G14" s="2" t="n"/>
-      <x:c r="H14" s="2" t="n"/>
-      <x:c r="I14" s="2" t="n"/>
-      <x:c r="J14" s="2" t="n"/>
+      <x:c r="A14" s="2"/>
+      <x:c r="B14" s="2"/>
+      <x:c r="C14" s="2"/>
+      <x:c r="D14" s="2"/>
+      <x:c r="E14" s="2"/>
+      <x:c r="F14" s="2"/>
+      <x:c r="G14" s="2"/>
+      <x:c r="H14" s="2"/>
+      <x:c r="I14" s="2"/>
+      <x:c r="J14" s="2"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Self-check score</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" s="11" t="str">
-        <x:f>COUNTIF(J6:J13,"Correct*")&amp;" of 8 complete"</x:f>
+      <x:c r="A15" s="131" t="str">
+        <x:v>Self-check score</x:v>
+      </x:c>
+      <x:c r="B15" s="131" t="str">
+        <x:f>COUNTIF(J6:J13,"Correct formula*")&amp;" of 8 complete"</x:f>
         <x:v>0 of 8 complete</x:v>
       </x:c>
-      <x:c r="C15" s="2" t="n"/>
-      <x:c r="D15" s="2" t="n"/>
-      <x:c r="E15" s="2" t="n"/>
-      <x:c r="F15" s="2" t="n"/>
-      <x:c r="G15" s="2" t="n"/>
-      <x:c r="H15" s="2" t="n"/>
-      <x:c r="I15" s="2" t="n"/>
-      <x:c r="J15" s="2" t="n"/>
+      <x:c r="C15" s="2"/>
+      <x:c r="D15" s="2"/>
+      <x:c r="E15" s="2"/>
+      <x:c r="F15" s="2"/>
+      <x:c r="G15" s="2"/>
+      <x:c r="H15" s="2"/>
+      <x:c r="I15" s="2"/>
+      <x:c r="J15" s="2"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1226,6 +1906,10 @@
     <x:mergeCell ref="A4:J4"/>
     <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="J6:J13">
+    <x:cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Correct formula"/>
+    <x:cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Check"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -1261,10 +1945,8 @@
       <x:c r="I1" s="15" t="n"/>
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
-      <x:c r="A2" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Read each scenario, enter the needed inputs into the yellow cells, then put the final answer in the blue cell. The grader checks the final answer; use Excel cash-flow signs where PMT or PV returns an outflow.</x:t>
-        </x:is>
+      <x:c r="A2" s="17" t="str">
+        <x:v>Complete two decision cases. Case 1: pairs, 8 minutes, loan-term evidence plus recommendation. Case 2: individual, 8 minutes, equal total contributions plus recommendation. Debrief by formula-bar audit and evidence share.</x:v>
       </x:c>
       <x:c r="B2" s="15" t="n"/>
       <x:c r="C2" s="15" t="n"/>
@@ -1302,45 +1984,29 @@
       <x:c r="I4" s="15" t="n"/>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">#</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Scenario</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Formula / Answer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hint</x:t>
-        </x:is>
+      <x:c r="A5" s="7" t="str">
+        <x:v>#</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="str">
+        <x:v>Scenario</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="str">
+        <x:v>Amount / Payment</x:v>
+      </x:c>
+      <x:c r="D5" s="7" t="str">
+        <x:v>Annual Rate</x:v>
+      </x:c>
+      <x:c r="E5" s="7" t="str">
+        <x:v>Years</x:v>
+      </x:c>
+      <x:c r="F5" s="7" t="str">
+        <x:v>Periods / Year</x:v>
+      </x:c>
+      <x:c r="G5" s="7" t="str">
+        <x:v>FORMULA / RESULT</x:v>
+      </x:c>
+      <x:c r="H5" s="7" t="str">
+        <x:v>Decision Evidence / Hint</x:v>
       </x:c>
       <x:c r="I5" s="7" t="str">
         <x:v>Instructor use - leave blank</x:v>
@@ -1350,316 +2016,276 @@
       <x:c r="A6" s="21" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the monthly PMT on a $320,000 mortgage at 6.5% annual interest over 30 years with 12 payments per year; report Excel PMT as a cash outflow.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="23" t="n"/>
-      <x:c r="D6" s="23" t="n"/>
-      <x:c r="E6" s="23" t="n"/>
-      <x:c r="F6" s="23" t="n"/>
-      <x:c r="G6" s="24" t="n"/>
-      <x:c r="H6" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Monthly rate and total months.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I6" s="12" t="n"/>
+      <x:c r="B6" s="22" t="str">
+        <x:v>30-year option: calculate the monthly mortgage payment.</x:v>
+      </x:c>
+      <x:c r="C6" s="146" t="n">
+        <x:v>320000</x:v>
+      </x:c>
+      <x:c r="D6" s="147" t="n">
+        <x:v>0.065</x:v>
+      </x:c>
+      <x:c r="E6" s="148" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F6" s="148" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G6" s="149"/>
+      <x:c r="H6" s="10" t="str">
+        <x:v>Use PMT with monthly timing; report the Excel cash-flow sign.</x:v>
+      </x:c>
+      <x:c r="I6" s="12"/>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
       <x:c r="A7" s="21" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the total paid over a $320,000 mortgage at 6.5% annual interest over 30 years with 12 payments per year.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="23" t="n"/>
-      <x:c r="D7" s="23" t="n"/>
-      <x:c r="E7" s="23" t="n"/>
-      <x:c r="F7" s="23" t="n"/>
-      <x:c r="G7" s="24" t="n"/>
-      <x:c r="H7" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ABS(payment) x total months.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I7" s="12" t="n"/>
+      <x:c r="B7" s="22" t="str">
+        <x:v>30-year option: calculate total interest.</x:v>
+      </x:c>
+      <x:c r="C7" s="146" t="n">
+        <x:v>320000</x:v>
+      </x:c>
+      <x:c r="D7" s="147" t="n">
+        <x:v>0.065</x:v>
+      </x:c>
+      <x:c r="E7" s="148" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F7" s="148" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G7" s="149"/>
+      <x:c r="H7" s="10" t="str">
+        <x:v>Reference the payment result and principal.</x:v>
+      </x:c>
+      <x:c r="I7" s="12"/>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
       <x:c r="A8" s="21" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B8" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find total interest on a $320,000 mortgage at 6.5% annual interest over 30 years with 12 payments per year.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="23" t="n"/>
-      <x:c r="D8" s="23" t="n"/>
-      <x:c r="E8" s="23" t="n"/>
-      <x:c r="F8" s="23" t="n"/>
-      <x:c r="G8" s="24" t="n"/>
-      <x:c r="H8" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Total paid minus original loan.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I8" s="12" t="n"/>
+      <x:c r="B8" s="22" t="str">
+        <x:v>10-year option: calculate the monthly mortgage payment.</x:v>
+      </x:c>
+      <x:c r="C8" s="146" t="n">
+        <x:v>320000</x:v>
+      </x:c>
+      <x:c r="D8" s="147" t="n">
+        <x:v>0.065</x:v>
+      </x:c>
+      <x:c r="E8" s="148" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F8" s="148" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G8" s="149"/>
+      <x:c r="H8" s="10" t="str">
+        <x:v>Use the same principal and rate with a shorter term.</x:v>
+      </x:c>
+      <x:c r="I8" s="12"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
       <x:c r="A9" s="21" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B9" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find total interest as a percent of the original $320,000 mortgage at 6.5% over 30 years.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="23" t="n"/>
-      <x:c r="D9" s="23" t="n"/>
-      <x:c r="E9" s="23" t="n"/>
-      <x:c r="F9" s="23" t="n"/>
-      <x:c r="G9" s="25" t="n"/>
-      <x:c r="H9" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Total interest divided by original principal.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I9" s="12" t="n"/>
+      <x:c r="B9" s="22" t="str">
+        <x:v>10-year option: calculate total interest.</x:v>
+      </x:c>
+      <x:c r="C9" s="146" t="n">
+        <x:v>320000</x:v>
+      </x:c>
+      <x:c r="D9" s="147" t="n">
+        <x:v>0.065</x:v>
+      </x:c>
+      <x:c r="E9" s="148" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F9" s="148" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G9" s="149"/>
+      <x:c r="H9" s="10" t="str">
+        <x:v>Reference the 10-year payment result and principal.</x:v>
+      </x:c>
+      <x:c r="I9" s="12"/>
     </x:row>
     <x:row r="10" ht="62" customHeight="1">
       <x:c r="A10" s="21" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B10" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the monthly PMT on the same $320,000 mortgage at 6.5% annual interest over 10 years with 12 payments per year; report Excel PMT as a cash outflow.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="23" t="n"/>
-      <x:c r="D10" s="23" t="n"/>
-      <x:c r="E10" s="23" t="n"/>
-      <x:c r="F10" s="23" t="n"/>
-      <x:c r="G10" s="24" t="n"/>
-      <x:c r="H10" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use the 10-year row from the total-interest table.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I10" s="12" t="n"/>
+      <x:c r="B10" s="22" t="str">
+        <x:v>Calculate interest saved by choosing 10 years instead of 30 years.</x:v>
+      </x:c>
+      <x:c r="C10" s="23"/>
+      <x:c r="D10" s="23"/>
+      <x:c r="E10" s="23"/>
+      <x:c r="F10" s="23"/>
+      <x:c r="G10" s="149"/>
+      <x:c r="H10" s="10" t="str">
+        <x:v>Reference the two total-interest cells.</x:v>
+      </x:c>
+      <x:c r="I10" s="12"/>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
       <x:c r="A11" s="21" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B11" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the interest saved by choosing the 10-year $320,000 mortgage at 6.5% instead of the 30-year mortgage at 6.5%.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="23" t="n"/>
-      <x:c r="D11" s="23" t="n"/>
-      <x:c r="E11" s="23" t="n"/>
-      <x:c r="F11" s="23" t="n"/>
-      <x:c r="G11" s="24" t="n"/>
-      <x:c r="H11" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Thirty-year interest minus ten-year interest.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I11" s="12" t="n"/>
+      <x:c r="B11" s="22" t="str">
+        <x:v>Recommendation: which term fits a client prioritizing monthly flexibility? Which fits minimizing lifetime cost?</x:v>
+      </x:c>
+      <x:c r="C11" s="23"/>
+      <x:c r="D11" s="23"/>
+      <x:c r="E11" s="23"/>
+      <x:c r="F11" s="23"/>
+      <x:c r="G11" s="149"/>
+      <x:c r="H11" s="10" t="str">
+        <x:v>Write two complete sentences using payment and interest evidence.</x:v>
+      </x:c>
+      <x:c r="I11" s="12"/>
     </x:row>
     <x:row r="12" ht="62" customHeight="1">
-      <x:c r="A12" s="21" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B12" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the monthly car payment for a $25,000 loan at 4.9% annual interest over 5 years with 12 payments per year; report Excel PMT as a cash outflow.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="23" t="n"/>
-      <x:c r="D12" s="23" t="n"/>
-      <x:c r="E12" s="23" t="n"/>
-      <x:c r="F12" s="23" t="n"/>
-      <x:c r="G12" s="24" t="n"/>
-      <x:c r="H12" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use PMT with monthly timing.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I12" s="12" t="n"/>
+      <x:c r="A12" s="141" t="str">
+        <x:v>Independent transfer - same $50,000 total contribution, different timing</x:v>
+      </x:c>
+      <x:c r="B12" s="142"/>
+      <x:c r="C12" s="141"/>
+      <x:c r="D12" s="141"/>
+      <x:c r="E12" s="141"/>
+      <x:c r="F12" s="141"/>
+      <x:c r="G12" s="151"/>
+      <x:c r="H12" s="144"/>
+      <x:c r="I12" s="144"/>
     </x:row>
     <x:row r="13" ht="34" customHeight="1">
       <x:c r="A13" s="21" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B13" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the future value of saving $200 per month at 6% annual return for 5 years with monthly deposits.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="23" t="n"/>
-      <x:c r="D13" s="23" t="n"/>
-      <x:c r="E13" s="23" t="n"/>
-      <x:c r="F13" s="23" t="n"/>
-      <x:c r="G13" s="24" t="n"/>
-      <x:c r="H13" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Monthly deposit is a negative pmt.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I13" s="12" t="n"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B13" s="22" t="str">
+        <x:v>Invest $50,000 today at 6% compounded monthly for 10 years.</x:v>
+      </x:c>
+      <x:c r="C13" s="146" t="n">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="D13" s="147" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="E13" s="148" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F13" s="148" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G13" s="149"/>
+      <x:c r="H13" s="10" t="str">
+        <x:v>Use FV with a lump-sum present value.</x:v>
+      </x:c>
+      <x:c r="I13" s="12"/>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
       <x:c r="A14" s="21" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B14" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the total monthly outflow for the $25,000 car loan at 4.9% over 5 years plus a $200 monthly savings goal.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="23" t="n"/>
-      <x:c r="D14" s="21" t="n"/>
-      <x:c r="E14" s="21" t="n"/>
-      <x:c r="F14" s="21" t="n"/>
-      <x:c r="G14" s="24" t="n"/>
-      <x:c r="H14" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Car payment as positive cash out plus savings deposit.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I14" s="12" t="n"/>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B14" s="22" t="str">
+        <x:v>Invest $416.6667 at each month-end for 10 years at 6%, monthly compounding.</x:v>
+      </x:c>
+      <x:c r="C14" s="146" t="n">
+        <x:v>416.6666667</x:v>
+      </x:c>
+      <x:c r="D14" s="147" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="E14" s="148" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F14" s="148" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G14" s="149"/>
+      <x:c r="H14" s="10" t="str">
+        <x:v>Use FV with a recurring payment; total nominal contributions equal $50,000.</x:v>
+      </x:c>
+      <x:c r="I14" s="12"/>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
       <x:c r="A15" s="21" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B15" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the monthly deposit required to reach $500,000 in 25 years at 7% annual return with monthly deposits; report Excel PMT as a cash outflow.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="23" t="n"/>
-      <x:c r="D15" s="23" t="n"/>
-      <x:c r="E15" s="23" t="n"/>
-      <x:c r="F15" s="23" t="n"/>
-      <x:c r="G15" s="24" t="n"/>
-      <x:c r="H15" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Solve for the monthly deposit; pv is zero.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I15" s="12" t="n"/>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B15" s="22" t="str">
+        <x:v>Calculate the ending-balance difference caused by timing.</x:v>
+      </x:c>
+      <x:c r="C15" s="23"/>
+      <x:c r="D15" s="23"/>
+      <x:c r="E15" s="23"/>
+      <x:c r="F15" s="23"/>
+      <x:c r="G15" s="149"/>
+      <x:c r="H15" s="10" t="str">
+        <x:v>Reference the two result cells.</x:v>
+      </x:c>
+      <x:c r="I15" s="12"/>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
       <x:c r="A16" s="21" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B16" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the present value of receiving $2,000 per month for 15 years at a 6% annual discount rate; report Excel PV using cash-flow signs.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C16" s="23" t="n"/>
-      <x:c r="D16" s="23" t="n"/>
-      <x:c r="E16" s="23" t="n"/>
-      <x:c r="F16" s="23" t="n"/>
-      <x:c r="G16" s="24" t="n"/>
-      <x:c r="H16" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Payment received is positive; PV result is negative.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I16" s="12" t="n"/>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B16" s="22" t="str">
+        <x:v>Recommendation: explain why equal contributions produce different ending balances.</x:v>
+      </x:c>
+      <x:c r="C16" s="23"/>
+      <x:c r="D16" s="23"/>
+      <x:c r="E16" s="23"/>
+      <x:c r="F16" s="23"/>
+      <x:c r="G16" s="149"/>
+      <x:c r="H16" s="10" t="str">
+        <x:v>Write two complete sentences using timing and dollar evidence.</x:v>
+      </x:c>
+      <x:c r="I16" s="12"/>
     </x:row>
     <x:row r="17" ht="34" customHeight="1">
-      <x:c r="A17" s="21" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B17" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the nominal value of receiving $2,000 per month for 15 years with 12 payments per year.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C17" s="23" t="n"/>
-      <x:c r="D17" s="21" t="n"/>
-      <x:c r="E17" s="23" t="n"/>
-      <x:c r="F17" s="23" t="n"/>
-      <x:c r="G17" s="24" t="n"/>
-      <x:c r="H17" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Monthly payment x years x 12.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I17" s="12" t="n"/>
+      <x:c r="A17" s="137"/>
+      <x:c r="B17" s="138"/>
+      <x:c r="C17" s="137"/>
+      <x:c r="D17" s="137"/>
+      <x:c r="E17" s="137"/>
+      <x:c r="F17" s="137"/>
+      <x:c r="G17" s="139"/>
+      <x:c r="H17" s="140"/>
+      <x:c r="I17" s="140"/>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
-      <x:c r="A18" s="21" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B18" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the discount from nominal value to present value for the $2,000 monthly payment stream over 15 years at 6%.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C18" s="21" t="n"/>
-      <x:c r="D18" s="21" t="n"/>
-      <x:c r="E18" s="21" t="n"/>
-      <x:c r="F18" s="21" t="n"/>
-      <x:c r="G18" s="24" t="n"/>
-      <x:c r="H18" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Nominal total minus absolute PV.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I18" s="12" t="n"/>
+      <x:c r="A18" s="137"/>
+      <x:c r="B18" s="138"/>
+      <x:c r="C18" s="137"/>
+      <x:c r="D18" s="137"/>
+      <x:c r="E18" s="137"/>
+      <x:c r="F18" s="137"/>
+      <x:c r="G18" s="139"/>
+      <x:c r="H18" s="140"/>
+      <x:c r="I18" s="140"/>
     </x:row>
     <x:row r="19" ht="34" customHeight="1">
-      <x:c r="A19" s="21" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B19" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the future value of a $50,000 lump sum invested at 6% annually for 10 years.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C19" s="23" t="n"/>
-      <x:c r="D19" s="23" t="n"/>
-      <x:c r="E19" s="23" t="n"/>
-      <x:c r="F19" s="23" t="n"/>
-      <x:c r="G19" s="24" t="n"/>
-      <x:c r="H19" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">This is the discussion prompt's lump sum.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I19" s="12" t="n"/>
+      <x:c r="A19" s="137"/>
+      <x:c r="B19" s="138"/>
+      <x:c r="C19" s="137"/>
+      <x:c r="D19" s="137"/>
+      <x:c r="E19" s="137"/>
+      <x:c r="F19" s="137"/>
+      <x:c r="G19" s="139"/>
+      <x:c r="H19" s="140"/>
+      <x:c r="I19" s="140"/>
     </x:row>
     <x:row r="20" ht="34" customHeight="1">
-      <x:c r="A20" s="21" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B20" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the future value of investing $500 per month for 10 years at 6% annual return with monthly deposits.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C20" s="23" t="n"/>
-      <x:c r="D20" s="23" t="n"/>
-      <x:c r="E20" s="23" t="n"/>
-      <x:c r="F20" s="23" t="n"/>
-      <x:c r="G20" s="24" t="n"/>
-      <x:c r="H20" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">This is the discussion prompt's monthly investment.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I20" s="12" t="n"/>
+      <x:c r="A20" s="137"/>
+      <x:c r="B20" s="138"/>
+      <x:c r="C20" s="137"/>
+      <x:c r="D20" s="137"/>
+      <x:c r="E20" s="137"/>
+      <x:c r="F20" s="137"/>
+      <x:c r="G20" s="139"/>
+      <x:c r="H20" s="140"/>
+      <x:c r="I20" s="140"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="2" t="n"/>
@@ -1677,6 +2303,7 @@
     <x:mergeCell ref="A1:I1"/>
     <x:mergeCell ref="A4:I4"/>
     <x:mergeCell ref="A2:I2"/>
+    <x:mergeCell ref="A12:I12"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1754,10 +2381,8 @@
           <x:t xml:space="preserve">Calculates the required monthly loan payment.</x:t>
         </x:is>
       </x:c>
-      <x:c r="D5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Result is usually negative because payment is an outflow.</x:t>
-        </x:is>
+      <x:c r="D5" s="2" t="str">
+        <x:v>The sign depends on perspective; a borrower-perspective payment is normally negative.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1841,30 +2466,32 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Annuity present value</x:t>
-        </x:is>
+      <x:c r="A10" s="2" t="str">
+        <x:v>Annuity present value</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
         <x:v>=PV(rate/12,years*12,pmt,0)</x:v>
       </x:c>
-      <x:c r="C10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Values a stream of equal payments today.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use the sign convention consistently.</x:t>
-        </x:is>
+      <x:c r="C10" s="2" t="str">
+        <x:v>Values a stream of equal payments today.</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="str">
+        <x:v>Use the sign convention consistently from one perspective.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="2" t="n"/>
-      <x:c r="B11" s="2" t="n"/>
-      <x:c r="C11" s="2" t="n"/>
-      <x:c r="D11" s="2" t="n"/>
+      <x:c r="A11" s="153" t="str">
+        <x:v>Cash-flow perspective</x:v>
+      </x:c>
+      <x:c r="B11" s="153" t="str">
+        <x:v>Opposite signs across pv, pmt, and fv</x:v>
+      </x:c>
+      <x:c r="C11" s="153" t="str">
+        <x:v>Shows what is paid out versus received from one stated viewpoint.</x:v>
+      </x:c>
+      <x:c r="D11" s="153" t="str">
+        <x:v>Do not describe a sign as universal without naming the perspective.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
